--- a/data/trans_orig/Q23_tabaco_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2007</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53950</t>
+          <t>53363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84600</t>
+          <t>84635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51991</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78823</t>
+          <t>79212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112087</t>
+          <t>111634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154938</t>
+          <t>153620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135418</t>
+          <t>133846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178878</t>
+          <t>175546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45685</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71661</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190087</t>
+          <t>189700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237682</t>
+          <t>239380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77714</t>
+          <t>76465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113380</t>
+          <t>113461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>22696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42781</t>
+          <t>43907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106644</t>
+          <t>106268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>145579</t>
+          <t>146236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>249859</t>
+          <t>248971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>297769</t>
+          <t>297815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67269</t>
+          <t>66489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302978</t>
+          <t>302280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>356968</t>
+          <t>357205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63154</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99229</t>
+          <t>98535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89545</t>
+          <t>89621</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127815</t>
+          <t>128333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161861</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>213828</t>
+          <t>214426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>264138</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>321506</t>
+          <t>323283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193383</t>
+          <t>193375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>239667</t>
+          <t>241020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>469718</t>
+          <t>471414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>547522</t>
+          <t>546887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208446</t>
+          <t>206477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259242</t>
+          <t>260333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97949</t>
+          <t>94306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137107</t>
+          <t>135226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316201</t>
+          <t>316693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>379850</t>
+          <t>381801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263504</t>
+          <t>262783</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>320553</t>
+          <t>317743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157934</t>
+          <t>158446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>204144</t>
+          <t>204070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432968</t>
+          <t>434643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>503240</t>
+          <t>503535</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>51138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56855</t>
+          <t>56575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65780</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99254</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>90303</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120815</t>
+          <t>121673</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>52768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78844</t>
+          <t>79584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>149386</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>189326</t>
+          <t>190765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>33888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60209</t>
+          <t>59455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43762</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98541</t>
+          <t>96859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59164</t>
+          <t>57955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57053</t>
+          <t>58398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89884</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>161377</t>
+          <t>159419</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216836</t>
+          <t>215021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191561</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243760</t>
+          <t>243171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>368854</t>
+          <t>367237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>448405</t>
+          <t>441739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>511314</t>
+          <t>513862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>590367</t>
+          <t>591289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>311032</t>
+          <t>308552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372441</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>845909</t>
+          <t>844605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946060</t>
+          <t>942683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>341400</t>
+          <t>340382</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>408477</t>
+          <t>408777</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>156441</t>
+          <t>154881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>204338</t>
+          <t>205037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>515594</t>
+          <t>511341</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>598091</t>
+          <t>592782</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>568525</t>
+          <t>572225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>650850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>816937</t>
+          <t>820550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2012</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82903</t>
+          <t>81000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121259</t>
+          <t>121115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93710</t>
+          <t>92710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152299</t>
+          <t>154377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205380</t>
+          <t>202849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137740</t>
+          <t>135497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183315</t>
+          <t>182395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79517</t>
+          <t>78993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198317</t>
+          <t>197415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249715</t>
+          <t>248053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89293</t>
+          <t>89094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126400</t>
+          <t>127628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28828</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54077</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126195</t>
+          <t>127718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>170288</t>
+          <t>171998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>285145</t>
+          <t>285226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>336453</t>
+          <t>337708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>65947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98472</t>
+          <t>97263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>367328</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427695</t>
+          <t>427402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>156578</t>
+          <t>155871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211171</t>
+          <t>209730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153900</t>
+          <t>153700</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200815</t>
+          <t>203930</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>328636</t>
+          <t>321765</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>397368</t>
+          <t>391866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315146</t>
+          <t>315450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377307</t>
+          <t>377704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244679</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299173</t>
+          <t>298803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572947</t>
+          <t>578769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>657088</t>
+          <t>660134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>190303</t>
+          <t>191923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245336</t>
+          <t>246584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133820</t>
+          <t>132555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180314</t>
+          <t>177851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339299</t>
+          <t>337801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>408939</t>
+          <t>409739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341163</t>
+          <t>338514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>406944</t>
+          <t>404797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220253</t>
+          <t>217665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>274932</t>
+          <t>273959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>575785</t>
+          <t>577024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>659702</t>
+          <t>663687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70339</t>
+          <t>69009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63699</t>
+          <t>63152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84238</t>
+          <t>83504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124125</t>
+          <t>123460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77355</t>
+          <t>77271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109051</t>
+          <t>107656</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65458</t>
+          <t>66991</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95856</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>152037</t>
+          <t>153460</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>195657</t>
+          <t>196431</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36064</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61344</t>
+          <t>60356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>50894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71150</t>
+          <t>68637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>101961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51683</t>
+          <t>53276</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69835</t>
+          <t>68799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105956</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>303285</t>
+          <t>295684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>374248</t>
+          <t>370189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>273655</t>
+          <t>272069</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339613</t>
+          <t>337775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>596750</t>
+          <t>593425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>687952</t>
+          <t>693804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>558111</t>
+          <t>553996</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>640281</t>
+          <t>639306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>379072</t>
+          <t>380444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>449377</t>
+          <t>450557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>963893</t>
+          <t>960841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1073639</t>
+          <t>1068187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>337838</t>
+          <t>336978</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>409863</t>
+          <t>408435</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>204267</t>
+          <t>205790</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>260608</t>
+          <t>261481</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>560464</t>
+          <t>559781</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>650510</t>
+          <t>654300</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>684862</t>
+          <t>688022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>777515</t>
+          <t>782753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>402629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1039640</t>
+          <t>1035795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1149899</t>
+          <t>1151495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2016</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77709</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>43076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65846</t>
+          <t>68276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97834</t>
+          <t>96867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137563</t>
+          <t>135725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>70306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103507</t>
+          <t>103093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>106592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>144225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72028</t>
+          <t>71944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105111</t>
+          <t>102833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90899</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126136</t>
+          <t>129022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175173</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216402</t>
+          <t>214334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229916</t>
+          <t>228065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>277018</t>
+          <t>278014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>152179</t>
+          <t>153262</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>201898</t>
+          <t>202004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170680</t>
+          <t>170942</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>221593</t>
+          <t>220816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>335263</t>
+          <t>335317</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>404403</t>
+          <t>406505</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278390</t>
+          <t>277791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>337899</t>
+          <t>338492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>245991</t>
+          <t>244465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>298285</t>
+          <t>298661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>540828</t>
+          <t>538269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>619820</t>
+          <t>621319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206896</t>
+          <t>207945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261812</t>
+          <t>262065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145260</t>
+          <t>146998</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191733</t>
+          <t>191489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367120</t>
+          <t>365249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>438139</t>
+          <t>436155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>354283</t>
+          <t>358427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>421990</t>
+          <t>423288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191457</t>
+          <t>189284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>240068</t>
+          <t>240951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>563040</t>
+          <t>564159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>642162</t>
+          <t>646084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>65030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62153</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80438</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118223</t>
+          <t>119208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57369</t>
+          <t>57066</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86747</t>
+          <t>86659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54905</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81870</t>
+          <t>82048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120674</t>
+          <t>119412</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>161492</t>
+          <t>161295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>33036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57252</t>
+          <t>58765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37919</t>
+          <t>39378</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63748</t>
+          <t>65553</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79671</t>
+          <t>78715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113045</t>
+          <t>113026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84483</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121087</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>257221</t>
+          <t>260492</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>321892</t>
+          <t>326999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>265610</t>
+          <t>267344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>327681</t>
+          <t>329339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>542959</t>
+          <t>545782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>630792</t>
+          <t>630612</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>428967</t>
+          <t>427757</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>501880</t>
+          <t>505684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349227</t>
+          <t>347872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>412918</t>
+          <t>414312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>799626</t>
+          <t>796938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>898696</t>
+          <t>895762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>332629</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>400240</t>
+          <t>398330</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212832</t>
+          <t>214954</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>267427</t>
+          <t>270953</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>561809</t>
+          <t>560597</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>650729</t>
+          <t>651485</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>592734</t>
+          <t>593427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>674617</t>
+          <t>674271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>291594</t>
+          <t>289723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>353450</t>
+          <t>353981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>897120</t>
+          <t>902029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1007602</t>
+          <t>1011252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2023</t>
+          <t>Población según la edad, en cuartiles, de inicio en el consumo de tabaco en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>37084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43022</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>66024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37175</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61146</t>
+          <t>60793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44357</t>
+          <t>44788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69779</t>
+          <t>69236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99044</t>
+          <t>99424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53812</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74746</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102690</t>
+          <t>103185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>145810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177608</t>
+          <t>178798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176280</t>
+          <t>174818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211955</t>
+          <t>212180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68338</t>
+          <t>63913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181365</t>
+          <t>178832</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105558</t>
+          <t>105905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140596</t>
+          <t>138719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161766</t>
+          <t>162864</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>306952</t>
+          <t>307824</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132092</t>
+          <t>121576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>322496</t>
+          <t>322669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179876</t>
+          <t>180467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221229</t>
+          <t>223780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>281941</t>
+          <t>267660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>525734</t>
+          <t>531674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281946</t>
+          <t>283633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>777118</t>
+          <t>782289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154596</t>
+          <t>156247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195334</t>
+          <t>196835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459366</t>
+          <t>456426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059038</t>
+          <t>1069086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148549</t>
+          <t>149402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>365816</t>
+          <t>366988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141122</t>
+          <t>142819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182347</t>
+          <t>183656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269085</t>
+          <t>268333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>520168</t>
+          <t>524979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56563</t>
+          <t>56078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91770</t>
+          <t>94133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47806</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69317</t>
+          <t>69018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110253</t>
+          <t>110212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155664</t>
+          <t>150093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55425</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84374</t>
+          <t>82537</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73899</t>
+          <t>73891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114850</t>
+          <t>113767</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>150039</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>37199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64834</t>
+          <t>64121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25138</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>41622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67734</t>
+          <t>67732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97903</t>
+          <t>100766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59634</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52136</t>
+          <t>52094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72084</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104902</t>
+          <t>105901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>136481</t>
+          <t>141206</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>285457</t>
+          <t>284761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183774</t>
+          <t>183010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>226657</t>
+          <t>228020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>313644</t>
+          <t>323766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>500166</t>
+          <t>495703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216186</t>
+          <t>219625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>438870</t>
+          <t>437842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274245</t>
+          <t>274677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322606</t>
+          <t>324678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463492</t>
+          <t>492931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>740985</t>
+          <t>742876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>388026</t>
+          <t>388156</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1016507</t>
+          <t>1017104</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>207753</t>
+          <t>207894</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>254776</t>
+          <t>255530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>615393</t>
+          <t>621348</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1363045</t>
+          <t>1225843</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>298395</t>
+          <t>294204</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>583959</t>
+          <t>587316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>211774</t>
+          <t>209671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>257936</t>
+          <t>258198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>515318</t>
+          <t>549260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>813850</t>
+          <t>809727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53363</t>
+          <t>54758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84635</t>
+          <t>84089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52207</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79212</t>
+          <t>78468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111634</t>
+          <t>114503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153620</t>
+          <t>156580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133846</t>
+          <t>130192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175546</t>
+          <t>174105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>44633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>73969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>189700</t>
+          <t>188369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239380</t>
+          <t>238441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113461</t>
+          <t>114611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>106343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146236</t>
+          <t>148654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248971</t>
+          <t>251498</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>297815</t>
+          <t>300354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>69010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302280</t>
+          <t>302439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64130</t>
+          <t>63290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98535</t>
+          <t>101144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89621</t>
+          <t>88536</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128333</t>
+          <t>126043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>162985</t>
+          <t>163013</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>214426</t>
+          <t>216033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>265045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323283</t>
+          <t>322199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193375</t>
+          <t>194228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241020</t>
+          <t>239997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>471414</t>
+          <t>471559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>546887</t>
+          <t>546318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206477</t>
+          <t>208404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260333</t>
+          <t>261985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94306</t>
+          <t>94542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>133878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316693</t>
+          <t>317040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381801</t>
+          <t>383913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>262783</t>
+          <t>260929</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>317743</t>
+          <t>316760</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158446</t>
+          <t>160613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>204070</t>
+          <t>205518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>434643</t>
+          <t>436596</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>503535</t>
+          <t>505075</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27457</t>
+          <t>27491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33004</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56575</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>64578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98885</t>
+          <t>97671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90303</t>
+          <t>86939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121673</t>
+          <t>119832</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52768</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79584</t>
+          <t>77790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>149386</t>
+          <t>149687</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>190765</t>
+          <t>190061</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>34932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59455</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43384</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>63372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96859</t>
+          <t>96550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57955</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,82 +2225,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>27477</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18736</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>39306</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>23,24%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>72562</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>58110</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>90310</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>14,4%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27477</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18821</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39077</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>72562</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>58398</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>88769</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159419</t>
+          <t>161911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215021</t>
+          <t>214988</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>191529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243171</t>
+          <t>241927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367237</t>
+          <t>366343</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441739</t>
+          <t>443958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>513862</t>
+          <t>513599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>591289</t>
+          <t>589328</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308552</t>
+          <t>308950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>369448</t>
+          <t>370274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>844605</t>
+          <t>844359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>942683</t>
+          <t>939954</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>340382</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>408777</t>
+          <t>408919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>154881</t>
+          <t>155785</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>205037</t>
+          <t>204075</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>511341</t>
+          <t>512424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>592782</t>
+          <t>597150</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>572225</t>
+          <t>567441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>650850</t>
+          <t>653171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>292311</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>820550</t>
+          <t>821881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>919160</t>
+          <t>921289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81000</t>
+          <t>80498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121115</t>
+          <t>121739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>62074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92710</t>
+          <t>91079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154377</t>
+          <t>153328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202849</t>
+          <t>202529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135497</t>
+          <t>137815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182395</t>
+          <t>182345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78993</t>
+          <t>79170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197415</t>
+          <t>198872</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248053</t>
+          <t>251508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89094</t>
+          <t>88926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127628</t>
+          <t>127085</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127718</t>
+          <t>125256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171998</t>
+          <t>172050</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>285226</t>
+          <t>286662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>337708</t>
+          <t>337176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65947</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97263</t>
+          <t>97200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364873</t>
+          <t>360504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427402</t>
+          <t>424188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155871</t>
+          <t>158295</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>209730</t>
+          <t>210012</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153700</t>
+          <t>154914</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203930</t>
+          <t>205318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>321765</t>
+          <t>325102</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>391866</t>
+          <t>395986</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315450</t>
+          <t>315072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377704</t>
+          <t>378994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244410</t>
+          <t>242425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>298803</t>
+          <t>300031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>578769</t>
+          <t>576384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>660134</t>
+          <t>656936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191923</t>
+          <t>191586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246584</t>
+          <t>246966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132555</t>
+          <t>133855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177851</t>
+          <t>181218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337801</t>
+          <t>342771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409739</t>
+          <t>407968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>338514</t>
+          <t>339079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>404797</t>
+          <t>405423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>217665</t>
+          <t>216377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>273959</t>
+          <t>273543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>577024</t>
+          <t>574698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663687</t>
+          <t>662419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40362</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69009</t>
+          <t>67979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>37427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>65218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83504</t>
+          <t>84448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123460</t>
+          <t>123800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77271</t>
+          <t>78723</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107656</t>
+          <t>110675</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66991</t>
+          <t>67720</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>96099</t>
+          <t>97875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>153460</t>
+          <t>151399</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196431</t>
+          <t>195861</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34432</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>60659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>27045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68637</t>
+          <t>69673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101961</t>
+          <t>104671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>35568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>61265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53276</t>
+          <t>52385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>70242</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104742</t>
+          <t>109267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>295684</t>
+          <t>299697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>370189</t>
+          <t>375975</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>272069</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>338105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>593425</t>
+          <t>591485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>693804</t>
+          <t>688507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>553996</t>
+          <t>554626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>639306</t>
+          <t>640380</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>380444</t>
+          <t>381882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>450557</t>
+          <t>450424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>960841</t>
+          <t>960205</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1068187</t>
+          <t>1074498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>336978</t>
+          <t>338229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>408435</t>
+          <t>412355</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>205790</t>
+          <t>206060</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>261481</t>
+          <t>262678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>559781</t>
+          <t>560275</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>654300</t>
+          <t>654894</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>688022</t>
+          <t>687633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>782753</t>
+          <t>776008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331478</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>402629</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1035795</t>
+          <t>1039296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1151495</t>
+          <t>1151292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79235</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43076</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68276</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96867</t>
+          <t>97830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135725</t>
+          <t>138070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70306</t>
+          <t>69944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103093</t>
+          <t>101912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106592</t>
+          <t>105706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144225</t>
+          <t>144299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71944</t>
+          <t>70249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102833</t>
+          <t>103083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>91730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>129022</t>
+          <t>128317</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174610</t>
+          <t>174428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214334</t>
+          <t>215036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>71471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>227110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>278014</t>
+          <t>276107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153262</t>
+          <t>152036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>201752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170942</t>
+          <t>170733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220816</t>
+          <t>221103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>335317</t>
+          <t>337809</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>406505</t>
+          <t>410713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>277791</t>
+          <t>278336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338492</t>
+          <t>337300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244465</t>
+          <t>244765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>298661</t>
+          <t>300033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>538269</t>
+          <t>539494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>621319</t>
+          <t>621711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207945</t>
+          <t>205354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262065</t>
+          <t>263246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>146505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191489</t>
+          <t>191673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>365249</t>
+          <t>365045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>436155</t>
+          <t>439911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358427</t>
+          <t>358998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>423288</t>
+          <t>422265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189284</t>
+          <t>190918</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>240951</t>
+          <t>239787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>564159</t>
+          <t>559614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>646084</t>
+          <t>642457</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65030</t>
+          <t>65351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>60999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82133</t>
+          <t>82251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119208</t>
+          <t>117406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86659</t>
+          <t>88430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55028</t>
+          <t>55230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82048</t>
+          <t>83126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119412</t>
+          <t>122389</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>161295</t>
+          <t>161133</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58765</t>
+          <t>57938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39378</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65553</t>
+          <t>64111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78715</t>
+          <t>77074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113026</t>
+          <t>113505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68544</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37078</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62722</t>
+          <t>63487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84261</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122666</t>
+          <t>122718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>260492</t>
+          <t>254032</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>326999</t>
+          <t>321106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>267344</t>
+          <t>266496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>329339</t>
+          <t>330806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>545782</t>
+          <t>539626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>630612</t>
+          <t>630572</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>427757</t>
+          <t>430040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>505684</t>
+          <t>505675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>347872</t>
+          <t>346650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>414312</t>
+          <t>415341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>796938</t>
+          <t>796740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>895762</t>
+          <t>893607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>332490</t>
+          <t>332016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>398330</t>
+          <t>397881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>214954</t>
+          <t>212283</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>270953</t>
+          <t>268103</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>560597</t>
+          <t>558560</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>651485</t>
+          <t>647804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>593427</t>
+          <t>596034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>674271</t>
+          <t>677659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>289723</t>
+          <t>289412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>353981</t>
+          <t>350416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>902029</t>
+          <t>905658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1011252</t>
+          <t>1013617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>21516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>40022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32211</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>58388</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43078</t>
+          <t>47354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66024</t>
+          <t>70782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47740</t>
+          <t>49791</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>62325</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44788</t>
+          <t>46995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69236</t>
+          <t>73578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99424</t>
+          <t>103832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64587</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52960</t>
+          <t>59215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77511</t>
+          <t>86571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30869</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>88078</t>
+          <t>98191</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74251</t>
+          <t>83837</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103185</t>
+          <t>114832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>161593</t>
+          <t>170168</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>145810</t>
+          <t>152241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178798</t>
+          <t>187254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>43387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>193643</t>
+          <t>204354</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174818</t>
+          <t>185308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212180</t>
+          <t>224408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>322320</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>322320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>322320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>449016</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>449016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>449016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>133447</t>
+          <t>147429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63913</t>
+          <t>124744</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178832</t>
+          <t>173060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121326</t>
+          <t>136135</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105905</t>
+          <t>119054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138719</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>254773</t>
+          <t>283564</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>162864</t>
+          <t>256313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>307824</t>
+          <t>317508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>243798</t>
+          <t>271400</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121576</t>
+          <t>242620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>322669</t>
+          <t>307365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>201004</t>
+          <t>217335</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180467</t>
+          <t>195533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223780</t>
+          <t>239861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>444802</t>
+          <t>488735</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267660</t>
+          <t>450605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>531674</t>
+          <t>527826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>473748</t>
+          <t>249892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283633</t>
+          <t>220444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>782289</t>
+          <t>279516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>175083</t>
+          <t>192341</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156247</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196835</t>
+          <t>217801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>648831</t>
+          <t>442233</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>456426</t>
+          <t>405921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069086</t>
+          <t>481815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>277869</t>
+          <t>297329</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149402</t>
+          <t>264567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366988</t>
+          <t>331320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>169881</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142819</t>
+          <t>150769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183656</t>
+          <t>191658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>439688</t>
+          <t>467210</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268333</t>
+          <t>429765</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>524979</t>
+          <t>503118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1128861</t>
+          <t>966050</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1128861</t>
+          <t>966050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1128861</t>
+          <t>966050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>659233</t>
+          <t>715692</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>659233</t>
+          <t>715692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>659233</t>
+          <t>715692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1788095</t>
+          <t>1681742</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1788095</t>
+          <t>1681742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1788095</t>
+          <t>1681742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70889</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56078</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94133</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>64554</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>77356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>128796</t>
+          <t>134237</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110212</t>
+          <t>116126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150093</t>
+          <t>155088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68928</t>
+          <t>80628</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82537</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62170</t>
+          <t>68196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>56918</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73891</t>
+          <t>80354</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131098</t>
+          <t>148824</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>129126</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>150039</t>
+          <t>167275</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37199</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64121</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>35188</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>26638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41622</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>82030</t>
+          <t>88530</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67732</t>
+          <t>72207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>108464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>50840</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52094</t>
+          <t>53723</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>88442</t>
+          <t>93912</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73657</t>
+          <t>78315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105901</t>
+          <t>112256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>254494</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>254494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>254494</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>193210</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>193210</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193210</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>465503</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>465503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>465503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>231327</t>
+          <t>246857</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141206</t>
+          <t>219615</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>284761</t>
+          <t>281405</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>204910</t>
+          <t>229332</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183010</t>
+          <t>206739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>228020</t>
+          <t>252800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>436237</t>
+          <t>476189</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>323766</t>
+          <t>439028</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>495703</t>
+          <t>514970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>360466</t>
+          <t>401820</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219625</t>
+          <t>364035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437842</t>
+          <t>441330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>299116</t>
+          <t>323823</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274677</t>
+          <t>296851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324678</t>
+          <t>352995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>659582</t>
+          <t>725643</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492931</t>
+          <t>682868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>742876</t>
+          <t>772028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>587786</t>
+          <t>375851</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>388156</t>
+          <t>340919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1017104</t>
+          <t>413902</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>231153</t>
+          <t>253103</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>229919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255530</t>
+          <t>280281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>818938</t>
+          <t>628954</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>621348</t>
+          <t>587622</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1225843</t>
+          <t>675885</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>487349</t>
+          <t>518337</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>294204</t>
+          <t>480198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>587316</t>
+          <t>556779</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>234424</t>
+          <t>247139</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209671</t>
+          <t>224465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>258198</t>
+          <t>275724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>765476</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>549260</t>
+          <t>718829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>809727</t>
+          <t>812747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1666928</t>
+          <t>1542864</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1666928</t>
+          <t>1542864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1666928</t>
+          <t>1542864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1053397</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1053397</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1053397</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2636530</t>
+          <t>2596262</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2636530</t>
+          <t>2596262</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2636530</t>
+          <t>2596262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
